--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:55</t>
+    <t xml:space="preserve">2026-09-24 01:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -996,13 +996,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="21">
@@ -1019,13 +1019,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="22">
@@ -1042,13 +1042,13 @@
         <v>30</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1105,19 +1105,19 @@
         <v>35</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.1</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.29</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="26">
@@ -1128,19 +1128,19 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="27">
@@ -1151,19 +1151,19 @@
         <v>35</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:44</t>
+    <t xml:space="preserve">2026-10-01 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2023_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:18</t>
+    <t xml:space="preserve">2026-10-05 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
